--- a/data/trans_dic/P34A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P34A_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre</t>
+          <t>Población que no realiza actividad física en su tiempo libre (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,3; 39,16</t>
+          <t>30,31; 39,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,48; 19,81</t>
+          <t>12,29; 19,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,13; 29,56</t>
+          <t>21,17; 29,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,98; 31,05</t>
+          <t>23,0; 31,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,08; 42,15</t>
+          <t>31,42; 42,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,01; 26,4</t>
+          <t>16,57; 26,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,48; 33,06</t>
+          <t>23,36; 33,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,97; 26,69</t>
+          <t>19,72; 26,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,13; 38,94</t>
+          <t>32,62; 39,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,2; 21,13</t>
+          <t>15,1; 21,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,53; 29,77</t>
+          <t>23,71; 29,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,61; 27,74</t>
+          <t>22,98; 28,21</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,02; 34,87</t>
+          <t>25,2; 35,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,3; 22,19</t>
+          <t>14,41; 22,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,46; 31,06</t>
+          <t>22,03; 30,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,74; 30,01</t>
+          <t>21,25; 30,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,92; 48,23</t>
+          <t>37,42; 47,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,76; 30,87</t>
+          <t>21,22; 31,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,5; 36,81</t>
+          <t>27,27; 37,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,13; 36,9</t>
+          <t>29,0; 36,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,81; 39,98</t>
+          <t>32,68; 40,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,27; 24,43</t>
+          <t>18,01; 24,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,31; 32,39</t>
+          <t>25,77; 32,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,92; 31,64</t>
+          <t>26,22; 31,86</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,94; 51,07</t>
+          <t>41,91; 50,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,61; 28,75</t>
+          <t>22,11; 29,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,65; 41,37</t>
+          <t>32,69; 41,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,08; 39,24</t>
+          <t>9,22; 39,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,04; 54,25</t>
+          <t>39,21; 54,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,0; 40,79</t>
+          <t>29,68; 41,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,16; 50,01</t>
+          <t>33,55; 49,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,64; 46,85</t>
+          <t>34,41; 46,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,62; 50,38</t>
+          <t>42,64; 50,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,54; 31,67</t>
+          <t>24,92; 31,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,45; 41,92</t>
+          <t>34,38; 42,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 39,54</t>
+          <t>10,04; 39,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,92; 49,76</t>
+          <t>44,16; 49,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,87; 28,21</t>
+          <t>22,83; 28,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,72; 41,45</t>
+          <t>35,9; 41,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,35; 41,57</t>
+          <t>35,28; 41,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,78; 51,1</t>
+          <t>43,44; 51,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,27; 33,81</t>
+          <t>27,52; 34,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,43; 46,26</t>
+          <t>39,2; 46,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,01; 40,48</t>
+          <t>15,99; 40,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45,13; 49,46</t>
+          <t>44,9; 49,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,55; 29,7</t>
+          <t>25,56; 29,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38,02; 42,49</t>
+          <t>37,96; 42,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,69; 39,68</t>
+          <t>22,53; 39,57</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,29; 56,22</t>
+          <t>45,49; 56,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,68; 32,17</t>
+          <t>24,54; 32,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,69; 45,23</t>
+          <t>37,0; 44,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,29; 47,89</t>
+          <t>38,27; 48,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,46; 58,43</t>
+          <t>49,8; 58,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,3; 40,1</t>
+          <t>33,41; 40,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,0; 51,78</t>
+          <t>44,2; 51,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,06; 51,76</t>
+          <t>34,19; 51,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49,3; 56,34</t>
+          <t>49,16; 56,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,44; 35,78</t>
+          <t>30,6; 35,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,86; 47,52</t>
+          <t>41,9; 47,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,5; 49,02</t>
+          <t>37,13; 48,73</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,23; 23,32</t>
+          <t>14,63; 24,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,96; 15,95</t>
+          <t>7,92; 15,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,15; 22,43</t>
+          <t>13,13; 22,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,08; 24,66</t>
+          <t>7,0; 24,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,28; 48,0</t>
+          <t>42,04; 47,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,67; 33,4</t>
+          <t>27,6; 33,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,64; 50,58</t>
+          <t>44,61; 50,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,96; 52,59</t>
+          <t>45,99; 52,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,49; 42,48</t>
+          <t>37,38; 42,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,39; 29,16</t>
+          <t>24,48; 29,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38,62; 43,96</t>
+          <t>38,4; 44,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,18; 43,94</t>
+          <t>37,15; 43,97</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,21; 42,74</t>
+          <t>39,21; 42,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,85; 23,94</t>
+          <t>21,06; 23,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,07; 35,28</t>
+          <t>32,1; 35,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,76; 33,9</t>
+          <t>24,06; 34,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,38; 47,97</t>
+          <t>44,48; 47,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,44; 32,51</t>
+          <t>29,4; 32,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,88; 44,43</t>
+          <t>40,83; 44,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30,9; 41,36</t>
+          <t>31,29; 41,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,49; 44,89</t>
+          <t>42,33; 44,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25,69; 27,88</t>
+          <t>25,69; 27,79</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37,26; 39,65</t>
+          <t>37,08; 39,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,78; 37,06</t>
+          <t>30,73; 37,16</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre</t>
+          <t>Población que no realiza actividad física en su tiempo libre (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>142302; 183892</t>
+          <t>142312; 184169</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54552; 86599</t>
+          <t>53725; 86688</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90669; 126855</t>
+          <t>90840; 127857</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115533; 156087</t>
+          <t>115610; 156899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>93208; 126405</t>
+          <t>94224; 127767</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53494; 83017</t>
+          <t>52108; 82216</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81494; 114739</t>
+          <t>81061; 114874</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>89372; 119433</t>
+          <t>88230; 118907</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>247259; 299604</t>
+          <t>250987; 305476</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114216; 158843</t>
+          <t>113504; 159970</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>182625; 231025</t>
+          <t>183991; 231684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>214854; 263545</t>
+          <t>218351; 268020</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90297; 125853</t>
+          <t>90968; 126967</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59890; 92912</t>
+          <t>60368; 94623</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80962; 117160</t>
+          <t>83097; 116011</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98296; 135700</t>
+          <t>96089; 135938</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>137834; 175299</t>
+          <t>136031; 174443</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70170; 104355</t>
+          <t>71716; 105899</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98661; 137052</t>
+          <t>101520; 138468</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>111458; 141164</t>
+          <t>110953; 141499</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>237688; 289610</t>
+          <t>236754; 290651</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138282; 184862</t>
+          <t>136325; 185898</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>189679; 242738</t>
+          <t>193170; 242142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>216343; 264089</t>
+          <t>218861; 265981</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>225524; 274612</t>
+          <t>225365; 272134</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135854; 180706</t>
+          <t>138964; 183250</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>170413; 215925</t>
+          <t>170590; 216776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60592; 261856</t>
+          <t>61548; 261384</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>64289; 89321</t>
+          <t>64567; 89938</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75436; 106099</t>
+          <t>77219; 107661</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56755; 83072</t>
+          <t>55737; 82464</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57768; 78117</t>
+          <t>57382; 77412</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>299356; 353887</t>
+          <t>299517; 351953</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>226962; 281455</t>
+          <t>221465; 279296</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>237020; 288422</t>
+          <t>236525; 291722</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>98423; 329791</t>
+          <t>83731; 329571</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>534358; 605519</t>
+          <t>537300; 606314</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>264837; 326681</t>
+          <t>264394; 324860</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>410669; 476560</t>
+          <t>412712; 478617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>364522; 428663</t>
+          <t>363758; 429817</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>309441; 361201</t>
+          <t>307051; 360463</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>209094; 259188</t>
+          <t>210990; 262904</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>325611; 382078</t>
+          <t>323709; 380855</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>166264; 395701</t>
+          <t>156345; 396440</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>868076; 951391</t>
+          <t>863633; 954337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>491813; 571594</t>
+          <t>491982; 574200</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>751111; 839328</t>
+          <t>749896; 840487</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>475889; 797087</t>
+          <t>452640; 794756</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>155273; 192743</t>
+          <t>155952; 194065</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>120886; 164241</t>
+          <t>125278; 165570</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>227743; 280765</t>
+          <t>229678; 279124</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181109; 226536</t>
+          <t>181019; 227505</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>274544; 324361</t>
+          <t>276463; 325627</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>253578; 305373</t>
+          <t>254444; 307500</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>324836; 382271</t>
+          <t>326332; 380816</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>285123; 433300</t>
+          <t>286157; 432992</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>442727; 505884</t>
+          <t>441394; 503726</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>387289; 455184</t>
+          <t>389220; 457323</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>568876; 645757</t>
+          <t>569396; 644261</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>491240; 642255</t>
+          <t>486407; 638352</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42320; 69342</t>
+          <t>43502; 71598</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21247; 42572</t>
+          <t>21132; 41629</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37748; 64398</t>
+          <t>37689; 65078</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17022; 59302</t>
+          <t>16830; 58535</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>519083; 589340</t>
+          <t>516174; 585323</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>306659; 370109</t>
+          <t>305915; 365981</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>483036; 547320</t>
+          <t>482644; 551156</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>348638; 398938</t>
+          <t>348819; 399139</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>571732; 647868</t>
+          <t>570101; 644370</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>335445; 401026</t>
+          <t>336640; 403330</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>528807; 601896</t>
+          <t>525764; 605471</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>371475; 438990</t>
+          <t>371097; 439279</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1264721; 1378501</t>
+          <t>1264464; 1381625</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>713231; 818951</t>
+          <t>720172; 817726</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1085640; 1194549</t>
+          <t>1086798; 1202082</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>800039; 1141227</t>
+          <t>809885; 1147027</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1472384; 1591396</t>
+          <t>1475555; 1589148</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1044707; 1153673</t>
+          <t>1043274; 1154818</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1443695; 1569061</t>
+          <t>1442034; 1565095</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1103162; 1476421</t>
+          <t>1117116; 1481180</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2779962; 2937072</t>
+          <t>2769556; 2929625</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1790230; 1943122</t>
+          <t>1790240; 1936669</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2577641; 2742784</t>
+          <t>2564872; 2737444</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2065499; 2570836</t>
+          <t>2131689; 2577856</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P34A_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,31; 39,22</t>
+          <t>30,68; 39,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,29; 19,83</t>
+          <t>12,27; 19,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,17; 29,8</t>
+          <t>21,21; 29,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,0; 31,21</t>
+          <t>22,99; 30,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,42; 42,61</t>
+          <t>30,87; 42,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,57; 26,15</t>
+          <t>17,04; 26,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,36; 33,1</t>
+          <t>23,74; 33,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,72; 26,57</t>
+          <t>20,32; 26,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,62; 39,7</t>
+          <t>32,29; 39,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,1; 21,28</t>
+          <t>15,27; 21,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,71; 29,85</t>
+          <t>23,39; 30,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,98; 28,21</t>
+          <t>22,78; 27,98</t>
         </is>
       </c>
     </row>
@@ -804,19 +804,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>25,56%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>42,75%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>25,55%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>42,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>31,89%</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,2; 35,17</t>
+          <t>25,3; 35,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,41; 22,59</t>
+          <t>14,33; 21,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,03; 30,75</t>
+          <t>21,73; 30,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,25; 30,06</t>
+          <t>21,75; 30,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,42; 47,99</t>
+          <t>37,53; 47,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,22; 31,33</t>
+          <t>21,1; 31,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,27; 37,2</t>
+          <t>26,87; 36,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,0; 36,99</t>
+          <t>28,7; 36,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,68; 40,12</t>
+          <t>32,66; 40,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 24,56</t>
+          <t>18,31; 24,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,77; 32,31</t>
+          <t>25,76; 32,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,22; 31,86</t>
+          <t>26,03; 31,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,91; 50,61</t>
+          <t>41,89; 50,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,11; 29,16</t>
+          <t>21,86; 29,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,69; 41,53</t>
+          <t>32,75; 41,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,22; 39,17</t>
+          <t>32,42; 41,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,21; 54,62</t>
+          <t>39,29; 53,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,68; 41,39</t>
+          <t>29,37; 41,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,55; 49,64</t>
+          <t>34,44; 50,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,41; 46,42</t>
+          <t>35,86; 47,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,64; 50,11</t>
+          <t>42,74; 50,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,92; 31,43</t>
+          <t>25,36; 31,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,38; 42,4</t>
+          <t>34,05; 41,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 39,52</t>
+          <t>34,81; 42,2</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,16; 49,83</t>
+          <t>44,14; 49,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,83; 28,05</t>
+          <t>22,77; 27,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,9; 41,63</t>
+          <t>35,79; 41,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,28; 41,68</t>
+          <t>35,3; 41,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,44; 51,0</t>
+          <t>43,83; 51,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,52; 34,29</t>
+          <t>27,23; 34,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,2; 46,12</t>
+          <t>39,4; 46,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,99; 40,55</t>
+          <t>37,28; 43,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44,9; 49,61</t>
+          <t>44,87; 49,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,56; 29,83</t>
+          <t>25,57; 29,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,96; 42,55</t>
+          <t>38,07; 42,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,53; 39,57</t>
+          <t>36,84; 41,09</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,49; 56,6</t>
+          <t>44,99; 55,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,54; 32,43</t>
+          <t>24,53; 32,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,0; 44,97</t>
+          <t>36,69; 44,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,27; 48,1</t>
+          <t>39,65; 48,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,8; 58,66</t>
+          <t>49,43; 58,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,41; 40,38</t>
+          <t>33,08; 40,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,2; 51,58</t>
+          <t>44,3; 51,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,19; 51,73</t>
+          <t>42,71; 48,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49,16; 56,1</t>
+          <t>49,25; 56,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,6; 35,95</t>
+          <t>30,85; 36,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,9; 47,41</t>
+          <t>41,9; 47,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,13; 48,73</t>
+          <t>42,55; 47,48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,74%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,63; 24,08</t>
+          <t>14,79; 23,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,92; 15,6</t>
+          <t>8,16; 16,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,13; 22,66</t>
+          <t>13,51; 22,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 24,34</t>
+          <t>6,6; 21,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,04; 47,67</t>
+          <t>42,19; 47,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,6; 33,02</t>
+          <t>27,72; 33,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,61; 50,94</t>
+          <t>44,44; 50,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,99; 52,62</t>
+          <t>45,37; 52,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,38; 42,25</t>
+          <t>37,51; 42,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,48; 29,33</t>
+          <t>24,39; 29,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38,4; 44,22</t>
+          <t>38,62; 44,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,15; 43,97</t>
+          <t>37,73; 44,03</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,21; 42,84</t>
+          <t>39,21; 42,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,06; 23,91</t>
+          <t>21,09; 23,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,1; 35,5</t>
+          <t>32,13; 35,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,06; 34,07</t>
+          <t>31,8; 35,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,48; 47,9</t>
+          <t>44,39; 47,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,4; 32,54</t>
+          <t>29,37; 32,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,83; 44,32</t>
+          <t>41,1; 44,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,29; 41,49</t>
+          <t>39,12; 42,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,33; 44,78</t>
+          <t>42,31; 44,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25,69; 27,79</t>
+          <t>25,65; 27,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37,08; 39,57</t>
+          <t>37,16; 39,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,73; 37,16</t>
+          <t>35,91; 38,26</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136174</t>
+          <t>147240</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>103807</t>
+          <t>114414</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>239981</t>
+          <t>261654</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>142312; 184169</t>
+          <t>144075; 184622</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53725; 86688</t>
+          <t>53628; 85350</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90840; 127857</t>
+          <t>91022; 127799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115610; 156899</t>
+          <t>126027; 169718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94224; 127767</t>
+          <t>92564; 126607</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52108; 82216</t>
+          <t>53577; 83638</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81061; 114874</t>
+          <t>82401; 116184</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>88230; 118907</t>
+          <t>99226; 131528</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>250987; 305476</t>
+          <t>248428; 301257</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113504; 159970</t>
+          <t>114795; 160193</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>183991; 231684</t>
+          <t>181509; 233156</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>218351; 268020</t>
+          <t>236078; 289991</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115531</t>
+          <t>123521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>125609</t>
+          <t>139356</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>241140</t>
+          <t>262876</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90968; 126967</t>
+          <t>91324; 126455</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60368; 94623</t>
+          <t>60001; 92057</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83097; 116011</t>
+          <t>81967; 116523</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96089; 135938</t>
+          <t>105087; 145045</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>136031; 174443</t>
+          <t>136399; 173762</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71716; 105899</t>
+          <t>71324; 104894</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>101520; 138468</t>
+          <t>100022; 137612</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>110953; 141499</t>
+          <t>121429; 154428</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>236754; 290651</t>
+          <t>236641; 289772</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>136325; 185898</t>
+          <t>138569; 187170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>193170; 242142</t>
+          <t>193042; 241860</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>218861; 265981</t>
+          <t>235946; 287431</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158681</t>
+          <t>174466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67619</t>
+          <t>77889</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>226300</t>
+          <t>252355</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>225365; 272134</t>
+          <t>225269; 272651</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>138964; 183250</t>
+          <t>137377; 183153</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>170590; 216776</t>
+          <t>170918; 216837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61548; 261384</t>
+          <t>152587; 196094</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>64567; 89938</t>
+          <t>64699; 88742</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77219; 107661</t>
+          <t>76394; 107214</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55737; 82464</t>
+          <t>57216; 84422</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57382; 77412</t>
+          <t>66971; 88859</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>299517; 351953</t>
+          <t>300171; 354362</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221465; 279296</t>
+          <t>225348; 279469</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>236525; 291722</t>
+          <t>234252; 284797</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>83731; 329571</t>
+          <t>228827; 277436</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>395419</t>
+          <t>427964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>306863</t>
+          <t>348259</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>702282</t>
+          <t>776223</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>537300; 606314</t>
+          <t>537051; 606581</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>264394; 324860</t>
+          <t>263702; 323329</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>412712; 478617</t>
+          <t>411465; 480920</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>363758; 429817</t>
+          <t>398024; 462534</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>307051; 360463</t>
+          <t>309817; 361691</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>210990; 262904</t>
+          <t>208760; 262012</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>323709; 380855</t>
+          <t>325419; 382436</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>156345; 396440</t>
+          <t>320623; 372619</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>863633; 954337</t>
+          <t>863172; 951588</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>491982; 574200</t>
+          <t>492143; 573385</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>749896; 840487</t>
+          <t>752041; 842475</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>452640; 794756</t>
+          <t>732288; 816787</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203725</t>
+          <t>249972</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>378699</t>
+          <t>378714</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>582423</t>
+          <t>628686</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>155952; 194065</t>
+          <t>154257; 191375</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>125278; 165570</t>
+          <t>125231; 165702</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>229678; 279124</t>
+          <t>227717; 276729</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181019; 227505</t>
+          <t>224301; 276738</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>276463; 325627</t>
+          <t>274369; 325366</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>254444; 307500</t>
+          <t>251897; 307539</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>326332; 380816</t>
+          <t>327016; 382989</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>286157; 432992</t>
+          <t>353681; 402923</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>441394; 503726</t>
+          <t>442228; 506402</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>389220; 457323</t>
+          <t>392420; 460617</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>569396; 644261</t>
+          <t>569362; 644676</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>486407; 638352</t>
+          <t>593082; 661724</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32184</t>
+          <t>28716</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>373544</t>
+          <t>410535</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>405728</t>
+          <t>439251</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>43502; 71598</t>
+          <t>43978; 70829</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21132; 41629</t>
+          <t>21766; 43194</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37689; 65078</t>
+          <t>38794; 65046</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16830; 58535</t>
+          <t>15658; 51351</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>516174; 585323</t>
+          <t>517959; 586831</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>305915; 365981</t>
+          <t>307166; 366688</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>482644; 551156</t>
+          <t>480818; 550144</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>348819; 399139</t>
+          <t>381523; 438583</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>570101; 644370</t>
+          <t>571996; 646503</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>336640; 403330</t>
+          <t>335362; 402017</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>525764; 605471</t>
+          <t>528759; 603720</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>371097; 439279</t>
+          <t>406749; 474647</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1041714</t>
+          <t>1151879</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1356142</t>
+          <t>1469167</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2397856</t>
+          <t>2621046</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1264464; 1381625</t>
+          <t>1264571; 1381502</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>720172; 817726</t>
+          <t>721199; 820342</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1086798; 1202082</t>
+          <t>1087997; 1201802</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>809885; 1147027</t>
+          <t>1091387; 1213379</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1475555; 1589148</t>
+          <t>1472806; 1585929</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1043274; 1154818</t>
+          <t>1042372; 1157073</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1442034; 1565095</t>
+          <t>1451567; 1572372</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1117116; 1481180</t>
+          <t>1418975; 1527585</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2769556; 2929625</t>
+          <t>2768484; 2932319</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1790240; 1936669</t>
+          <t>1787521; 1939629</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2564872; 2737444</t>
+          <t>2570455; 2735703</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2131689; 2577856</t>
+          <t>2534899; 2701409</t>
         </is>
       </c>
     </row>
